--- a/examples/excel/charts/charts-demo.xlsx
+++ b/examples/excel/charts/charts-demo.xlsx
@@ -1030,7 +1030,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R2d2f2dbc091b4dc6"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Radcf55753bf94625"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1060,7 +1060,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R576f36af273242a2"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rbf6bcd9029ae4e51"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1090,7 +1090,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R05b3ce2005f94eed"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R61ac80241cdf4c7d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1120,7 +1120,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rac9cf1de646d40dd"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rdc5216fe7d9245b5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1150,7 +1150,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R84aad00685b5475f"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R612dfdfc0ff949f9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1180,7 +1180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rc18da4b2ae074cb0"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R23ec0e43a7e043ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1189,8 +1189,117 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="str">
@@ -1414,6 +1523,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aec4e60af8d4980"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c463e6fd4294408"/>
 </x:worksheet>
 </file>